--- a/OnTrack TCM - Test Suites.xlsx
+++ b/OnTrack TCM - Test Suites.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\codes\softeng\rotten-potato-TCM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D945A16-89FF-45F7-8292-D56DB0D29EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD8F52ED-2876-4EB1-8A84-D047E642405B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Suites" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="91">
+  <si>
+    <t/>
+  </si>
   <si>
     <t>Test Schedule</t>
   </si>
@@ -88,9 +91,15 @@
     <t>COMM-0002 : Commissioner Posts Open Request</t>
   </si>
   <si>
+    <t>BUG-005</t>
+  </si>
+  <si>
     <t>COMM-0003 : Artist Test Account Setup</t>
   </si>
   <si>
+    <t>BUG-006</t>
+  </si>
+  <si>
     <t>COMM-0004 : Artist Sends Commission Offer</t>
   </si>
   <si>
@@ -127,12 +136,6 @@
     <t>MSG-0008 : Sidebar Modal Incoming Message Notification</t>
   </si>
   <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>draft</t>
-  </si>
-  <si>
     <t>Discovery-and-Navigation</t>
   </si>
   <si>
@@ -145,9 +148,15 @@
     <t>SRCH-0003 : Result Card Summary Overlay</t>
   </si>
   <si>
+    <t>BUG-0002</t>
+  </si>
+  <si>
     <t>SRCH-0004 : Target Search Node Routing Validation</t>
   </si>
   <si>
+    <t>BUG-0003</t>
+  </si>
+  <si>
     <t>Financials</t>
   </si>
   <si>
@@ -187,6 +196,12 @@
     <t>PAY-0010 : Commission Deposit Paid Commit</t>
   </si>
   <si>
+    <t>NOT RUN</t>
+  </si>
+  <si>
+    <t>BUG-007</t>
+  </si>
+  <si>
     <t>PAY-0011 : Artist Marks Commission Ready for Final Payment</t>
   </si>
   <si>
@@ -217,6 +232,9 @@
     <t>PRF-0002 : Profile Display (Edge Cases)</t>
   </si>
   <si>
+    <t>BUG-004</t>
+  </si>
+  <si>
     <t>PRF-0003 : Edit Profile (Persistence)</t>
   </si>
   <si>
@@ -256,34 +274,25 @@
     <t>REV-0005 : Rating Metadata and Price Cohesion</t>
   </si>
   <si>
-    <t>Social-and-Community</t>
-  </si>
-  <si>
-    <t>FEED-0001 : Canvas Content Creator Panel Ingestion</t>
-  </si>
-  <si>
-    <t>FEED-0002 : Image Canvas Creation and Timeline Injection</t>
-  </si>
-  <si>
-    <t>FEED-0003 : Reaction Counter Mutators and Web Notification Dispatches</t>
-  </si>
-  <si>
-    <t>FEED-0004 : Media Post Dialogue Expansion</t>
-  </si>
-  <si>
-    <t>FEED-0005 : Text Comment Injection Pipeline</t>
-  </si>
-  <si>
-    <t>FEED-0006 : Asset Cross-Posting Share Workflows</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>BUG-0003</t>
-  </si>
-  <si>
-    <t>BUG-0002</t>
+    <t>FEED-001: Social and Community Testing - Artwork Publication</t>
+  </si>
+  <si>
+    <t>FEED-002: Social and Community Testing - Artwork Publication</t>
+  </si>
+  <si>
+    <t>FEED-003: Social and Community Testing - Reaction Handlers</t>
+  </si>
+  <si>
+    <t>FEED-004: Social and Community Testing - Social Interaction Hooks</t>
+  </si>
+  <si>
+    <t>FEED-005: Social and Community Testing - Social Interaction Hooks</t>
+  </si>
+  <si>
+    <t>FEED-006: Social and Community Testing - Social Interaction Hooks</t>
+  </si>
+  <si>
+    <t>Social and Community</t>
   </si>
 </sst>
 </file>
@@ -293,7 +302,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -306,8 +315,21 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -326,6 +348,12 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -336,19 +364,29 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{4229D7B3-2902-4A37-BE2F-44EDFB08648F}"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -677,1141 +715,1159 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="85" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="2" max="2" width="15" style="7" customWidth="1"/>
+    <col min="3" max="3" width="17" style="7" customWidth="1"/>
+    <col min="4" max="4" width="19" style="7" customWidth="1"/>
     <col min="5" max="6" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="B2" s="6"/>
+      <c r="D2" s="6"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="D3" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="D3" s="6"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
+      <c r="B4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="B10" s="6"/>
+      <c r="D10" s="6"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="D11" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="D11" s="6"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="B12" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F13" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F14" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="B18" s="6"/>
+      <c r="D18" s="6"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="D19" s="2"/>
+        <v>29</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="D19" s="6"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>20</v>
+        <v>31</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>20</v>
+        <v>34</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>20</v>
+        <v>35</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="2">
-        <v>46120</v>
-      </c>
-      <c r="C26" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="2">
+        <v>37</v>
+      </c>
+      <c r="B27" s="6">
         <v>46120</v>
       </c>
-      <c r="C27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>20</v>
+      <c r="C27" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="6">
+        <v>46179</v>
       </c>
       <c r="E27" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="2"/>
-      <c r="D28" s="2"/>
+      <c r="B28" s="6"/>
+      <c r="D28" s="6"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="2"/>
-      <c r="D29" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="B29" s="6"/>
+      <c r="D29" s="6"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="2">
+        <v>39</v>
+      </c>
+      <c r="B30" s="6">
         <v>46120</v>
       </c>
-      <c r="C30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="2">
+      <c r="C30" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="6">
         <v>46179</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="2">
+        <v>40</v>
+      </c>
+      <c r="B31" s="6">
         <v>46120</v>
       </c>
-      <c r="C31" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="2">
+      <c r="C31" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="6">
         <v>46179</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="2">
+        <v>41</v>
+      </c>
+      <c r="B32" s="6">
         <v>46120</v>
       </c>
-      <c r="C32" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="2">
+      <c r="C32" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="6">
         <v>46179</v>
       </c>
       <c r="E32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="2">
+        <v>43</v>
+      </c>
+      <c r="B33" s="6">
         <v>46120</v>
       </c>
-      <c r="C33" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="2">
+      <c r="C33" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="6">
         <v>46179</v>
       </c>
       <c r="E33" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B34" s="2"/>
-      <c r="D34" s="2"/>
+      <c r="B34" s="6"/>
+      <c r="D34" s="6"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="2"/>
-      <c r="D35" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="B35" s="6"/>
+      <c r="D35" s="6"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E36" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>46</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" t="s">
-        <v>44</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E37" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>45</v>
+      <c r="D38" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E38" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>48</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" t="s">
-        <v>44</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>45</v>
+        <v>51</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E39" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>49</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" t="s">
-        <v>44</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E40" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>50</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" t="s">
-        <v>44</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E41" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>51</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" t="s">
-        <v>44</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E42" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>52</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" t="s">
-        <v>44</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>45</v>
+        <v>55</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E43" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>53</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" t="s">
-        <v>44</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>45</v>
+        <v>56</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E44" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>54</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" t="s">
-        <v>44</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E45" t="s">
-        <v>36</v>
+        <v>57</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F45" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>55</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" t="s">
-        <v>44</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E46" t="s">
-        <v>36</v>
+        <v>60</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F46" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>56</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" t="s">
-        <v>44</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E47" t="s">
-        <v>36</v>
+        <v>61</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F47" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B48" s="2"/>
-      <c r="D48" s="2"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B48" s="6"/>
+      <c r="D48" s="6"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B49" s="2"/>
-      <c r="D49" s="2"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+      <c r="B49" s="6"/>
+      <c r="D49" s="6"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>58</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" t="s">
-        <v>44</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>45</v>
+        <v>63</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E50" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>59</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" t="s">
-        <v>44</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>45</v>
+        <v>64</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E51" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>60</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" t="s">
-        <v>44</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>45</v>
+        <v>65</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E52" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B53" s="2"/>
-      <c r="D53" s="2"/>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B53" s="6"/>
+      <c r="D53" s="6"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="2"/>
-      <c r="D54" s="2"/>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+      <c r="B54" s="6"/>
+      <c r="D54" s="6"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>62</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C55" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>20</v>
+        <v>67</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E55" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>64</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>20</v>
+        <v>69</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E56" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="F56" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>65</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C57" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>20</v>
+        <v>71</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E57" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>66</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>20</v>
+        <v>72</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E58" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>67</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C59" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>20</v>
+        <v>73</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E59" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>74</v>
+      </c>
+      <c r="B60" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C60" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>20</v>
+      <c r="C60" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E60" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>69</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C61" t="s">
-        <v>8</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>20</v>
+        <v>75</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E61" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>70</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C62" t="s">
-        <v>8</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>20</v>
+        <v>76</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E62" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>71</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C63" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>20</v>
+        <v>77</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E63" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B64" s="2"/>
-      <c r="D64" s="2"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B64" s="6"/>
+      <c r="D64" s="6"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B65" s="2"/>
-      <c r="D65" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="B65" s="6"/>
+      <c r="D65" s="6"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>73</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C66" t="s">
-        <v>35</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>35</v>
+        <v>79</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E66" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>74</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C67" t="s">
-        <v>35</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>35</v>
+        <v>80</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E67" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>75</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C68" t="s">
-        <v>35</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>35</v>
+        <v>81</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E68" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>76</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C69" t="s">
-        <v>35</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E69" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>77</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C70" t="s">
-        <v>35</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>35</v>
+        <v>83</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E70" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B71" s="2"/>
-      <c r="D71" s="2"/>
+      <c r="B71" s="6"/>
+      <c r="D71" s="6"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B72" s="2"/>
-      <c r="D72" s="2"/>
+      <c r="A72" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B72" s="6"/>
+      <c r="D72" s="6"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>79</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C73" t="s">
-        <v>35</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>35</v>
+        <v>84</v>
+      </c>
+      <c r="B73" s="6">
+        <v>46113</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" s="6">
+        <v>46183</v>
       </c>
       <c r="E73" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>80</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C74" t="s">
-        <v>35</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>35</v>
+        <v>85</v>
+      </c>
+      <c r="B74" s="6">
+        <v>46113</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74" s="6">
+        <v>46183</v>
       </c>
       <c r="E74" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>81</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C75" t="s">
-        <v>35</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>35</v>
+        <v>86</v>
+      </c>
+      <c r="B75" s="6">
+        <v>46113</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" s="6">
+        <v>46183</v>
       </c>
       <c r="E75" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>82</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C76" t="s">
-        <v>35</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>35</v>
+        <v>87</v>
+      </c>
+      <c r="B76" s="6">
+        <v>46113</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D76" s="6">
+        <v>46183</v>
       </c>
       <c r="E76" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>83</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C77" t="s">
-        <v>35</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>35</v>
+        <v>88</v>
+      </c>
+      <c r="B77" s="6">
+        <v>46113</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D77" s="6">
+        <v>46183</v>
       </c>
       <c r="E77" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>84</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C78" t="s">
-        <v>35</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>35</v>
+        <v>89</v>
+      </c>
+      <c r="B78" s="6">
+        <v>46113</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D78" s="6">
+        <v>46183</v>
       </c>
       <c r="E78" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
